--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Madhuravoyal_to_SilkBoard/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Madhuravoyal_to_SilkBoard/Average/Master_Results.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Phase_Difference_Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Descriptive_Statistics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Route_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Plot_Audit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -755,79 +754,79 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18.67793333333333</v>
+        <v>345.6166666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>29.6565</v>
+        <v>358.3974333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>11.42391390088974</v>
+        <v>320.3395097107276</v>
       </c>
       <c r="J2" t="n">
-        <v>11.63657856259103</v>
+        <v>320.689018034049</v>
       </c>
       <c r="K2" t="n">
-        <v>55.44692920604529</v>
+        <v>64.61675662785962</v>
       </c>
       <c r="L2" t="n">
-        <v>59.58783215117909</v>
+        <v>59.67911560660773</v>
       </c>
       <c r="M2" t="n">
-        <v>-10.97856666666667</v>
+        <v>-12.78076666666664</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2126646617012895</v>
+        <v>-0.3495083233214018</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.140902945133803</v>
+        <v>4.937641021251885</v>
       </c>
       <c r="P2" t="n">
-        <v>-11.5</v>
+        <v>-25.76666666666666</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
       <c r="W2" t="n">
-        <v>6.55</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="X2" t="n">
-        <v>18.05</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>-11.5</v>
+        <v>-25.41666666666666</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2163028850735744</v>
+        <v>0.4696266909337409</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1098089982133633</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1064938868602111</v>
+        <v>0.1222862675192465</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -839,86 +838,86 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-3.416666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.2646788011201056</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.4374014031543842</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>-0.1727226020342786</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.5</v>
+        <v>49.31666666666667</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.2872</v>
+        <v>62.08705</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.7871999999999999</v>
+        <v>-12.77038333333333</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.38371396280334</v>
+        <v>46.82863918427439</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.054887036688835</v>
+        <v>58.41038144450143</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.6711730738854951</v>
+        <v>-11.58174226022705</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.533333333333333</v>
+        <v>44.58333333333334</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.433333333333333</v>
+        <v>50.53333333333333</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1000000000000001</v>
+        <v>-5.949999999999989</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.971912446606221</v>
+        <v>41.95380970861748</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.822408693852921</v>
+        <v>47.46435945988381</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.8504962472467001</v>
+        <v>-5.510549751266332</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.0946</v>
+        <v>202.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.885966666666667</v>
+        <v>205.3603833333333</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.208633333333333</v>
+        <v>-3.210383333333283</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.851984606406608</v>
+        <v>230.5006829298171</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.649473833835908</v>
+        <v>214.0295353030949</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.2025107725707</v>
+        <v>16.4711476267222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,164 +936,164 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_036_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>14.8788</v>
+        <v>477.62115</v>
       </c>
       <c r="H3" t="n">
-        <v>16.75645</v>
+        <v>368.0833333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>12.73848083938423</v>
+        <v>326.4581126643001</v>
       </c>
       <c r="J3" t="n">
-        <v>12.6496249595659</v>
+        <v>326.5906174282528</v>
       </c>
       <c r="K3" t="n">
-        <v>51.36898475435208</v>
+        <v>53.20517022732241</v>
       </c>
       <c r="L3" t="n">
-        <v>45.29464758788131</v>
+        <v>59.00405914179443</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.877650000000001</v>
+        <v>109.5378166666667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08885587981833076</v>
+        <v>-0.1325047639527384</v>
       </c>
       <c r="O3" t="n">
-        <v>6.074337166470769</v>
+        <v>-5.798888914472016</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>33.76333333333334</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.07340092752195768</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.07340092752195768</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>46.84666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>10.86333333333334</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.7018049624302896</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.3544645390157952</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.04555431783926916</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.04555431783926916</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>14.68333333333333</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.08333333333333333</v>
+        <v>10.51666666666666</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.402436801450748</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01248000402488661</v>
+        <v>0.4545741125317043</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.01248000402488661</v>
+        <v>0.9478626889190437</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.1</v>
+        <v>52.48333333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.266666666666667</v>
+        <v>65.36666666666666</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.166666666666667</v>
+        <v>-12.88333333333333</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.57280616355066</v>
+        <v>43.07361049641583</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.59336123238131</v>
+        <v>60.40870474559063</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.02055506883065</v>
+        <v>-17.3350942491748</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.43445</v>
+        <v>45.11666666666667</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.623083333333333</v>
+        <v>52.46666666666667</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.1886333333333332</v>
+        <v>-7.350000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.851109043655713</v>
+        <v>38.72857510577813</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.975517359737947</v>
+        <v>48.51069404037401</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.124408316082234</v>
+        <v>-9.782118934595886</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.34435</v>
+        <v>254.94115</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.78336666666667</v>
+        <v>209.75</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.4390166666666691</v>
+        <v>45.19114999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.314565632177855</v>
+        <v>242.4327300528639</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.068266363421753</v>
+        <v>216.869304106342</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.246299268756102</v>
+        <v>25.56342594652187</v>
       </c>
     </row>
   </sheetData>
@@ -1165,22 +1164,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
     </row>
     <row r="3">
@@ -1195,22 +1194,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.55</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>18.05</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.5</v>
+        <v>-25.41666666666666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2163028850735744</v>
+        <v>0.4696266909337409</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1098089982133633</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1064938868602111</v>
+        <v>0.1222862675192465</v>
       </c>
     </row>
     <row r="4">
@@ -1228,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1255,22 +1254,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-3.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.2646788011201056</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.4374014031543842</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.1727226020342786</v>
       </c>
     </row>
     <row r="6">
@@ -1285,22 +1284,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>49.31666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2872</v>
+        <v>62.08705</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7871999999999999</v>
+        <v>-12.77038333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>2.38371396280334</v>
+        <v>46.82863918427439</v>
       </c>
       <c r="G6" t="n">
-        <v>3.054887036688835</v>
+        <v>58.41038144450143</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6711730738854951</v>
+        <v>-11.58174226022705</v>
       </c>
     </row>
     <row r="7">
@@ -1315,22 +1314,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.533333333333333</v>
+        <v>44.58333333333334</v>
       </c>
       <c r="D7" t="n">
-        <v>3.433333333333333</v>
+        <v>50.53333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1000000000000001</v>
+        <v>-5.949999999999989</v>
       </c>
       <c r="F7" t="n">
-        <v>1.971912446606221</v>
+        <v>41.95380970861748</v>
       </c>
       <c r="G7" t="n">
-        <v>2.822408693852921</v>
+        <v>47.46435945988381</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8504962472467001</v>
+        <v>-5.510549751266332</v>
       </c>
     </row>
     <row r="8">
@@ -1345,28 +1344,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.0946</v>
+        <v>202.15</v>
       </c>
       <c r="D8" t="n">
-        <v>4.885966666666667</v>
+        <v>205.3603833333333</v>
       </c>
       <c r="E8" t="n">
-        <v>1.208633333333333</v>
+        <v>-3.210383333333283</v>
       </c>
       <c r="F8" t="n">
-        <v>6.851984606406608</v>
+        <v>230.5006829298171</v>
       </c>
       <c r="G8" t="n">
-        <v>5.649473833835908</v>
+        <v>214.0295353030949</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2025107725707</v>
+        <v>16.4711476267222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1375,28 +1374,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.07340092752195768</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.07340092752195768</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1405,28 +1404,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>46.84666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>10.86333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.7018049624302896</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.3544645390157952</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1435,28 +1434,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.04555431783926916</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.04555431783926916</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1465,28 +1464,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>14.68333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08333333333333333</v>
+        <v>10.51666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.402436801450748</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01248000402488661</v>
+        <v>0.4545741125317043</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.01248000402488661</v>
+        <v>0.9478626889190437</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1495,28 +1494,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.1</v>
+        <v>52.48333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>3.266666666666667</v>
+        <v>65.36666666666666</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.166666666666667</v>
+        <v>-12.88333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>1.57280616355066</v>
+        <v>43.07361049641583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.59336123238131</v>
+        <v>60.40870474559063</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.02055506883065</v>
+        <v>-17.3350942491748</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1525,28 +1524,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.43445</v>
+        <v>45.11666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>2.623083333333333</v>
+        <v>52.46666666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1886333333333332</v>
+        <v>-7.350000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.851109043655713</v>
+        <v>38.72857510577813</v>
       </c>
       <c r="G14" t="n">
-        <v>1.975517359737947</v>
+        <v>48.51069404037401</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.124408316082234</v>
+        <v>-9.782118934595886</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_036</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1555,22 +1554,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.34435</v>
+        <v>254.94115</v>
       </c>
       <c r="D15" t="n">
-        <v>10.78336666666667</v>
+        <v>209.75</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4390166666666691</v>
+        <v>45.19114999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>9.314565632177855</v>
+        <v>242.4327300528639</v>
       </c>
       <c r="G15" t="n">
-        <v>8.068266363421753</v>
+        <v>216.869304106342</v>
       </c>
       <c r="H15" t="n">
-        <v>1.246299268756102</v>
+        <v>25.56342594652187</v>
       </c>
     </row>
   </sheetData>
@@ -1631,19 +1630,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.1977366617433377</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1656,22 +1655,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.275</v>
+        <v>28.70666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>9.025</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.75</v>
+        <v>-7.276666666666657</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.75</v>
+        <v>-7.276666666666657</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1081514425367872</v>
+        <v>0.5857158266820153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05490449910668165</v>
+        <v>0.3473404234144944</v>
       </c>
     </row>
     <row r="4">
@@ -1681,19 +1680,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>11.625</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>11.275</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>11.275</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.02277715891963458</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1706,22 +1705,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>7.674999999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04166666666666666</v>
+        <v>4.125</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04166666666666666</v>
+        <v>3.549999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04166666666666666</v>
+        <v>3.549999999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.8335578012854268</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006240002012443305</v>
+        <v>0.4459877578430442</v>
       </c>
     </row>
     <row r="6">
@@ -1731,22 +1730,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.3</v>
+        <v>50.9</v>
       </c>
       <c r="C6" t="n">
-        <v>3.276933333333333</v>
+        <v>63.72685833333333</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9769333333333334</v>
+        <v>-12.82685833333333</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9769333333333334</v>
+        <v>-12.82685833333333</v>
       </c>
       <c r="F6" t="n">
-        <v>1.978260063177</v>
+        <v>44.95112484034511</v>
       </c>
       <c r="G6" t="n">
-        <v>2.824124134535072</v>
+        <v>59.40954309504603</v>
       </c>
     </row>
     <row r="7">
@@ -1756,22 +1755,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.983891666666667</v>
+        <v>44.85000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>3.028208333333333</v>
+        <v>51.5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04431666666666656</v>
+        <v>-6.649999999999995</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04431666666666656</v>
+        <v>-6.649999999999995</v>
       </c>
       <c r="F7" t="n">
-        <v>1.911510745130967</v>
+        <v>40.3411924071978</v>
       </c>
       <c r="G7" t="n">
-        <v>2.398963026795434</v>
+        <v>47.98752675012891</v>
       </c>
     </row>
     <row r="8">
@@ -1781,22 +1780,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.219474999999999</v>
+        <v>228.545575</v>
       </c>
       <c r="C8" t="n">
-        <v>7.834666666666668</v>
+        <v>207.5551916666666</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3848083333333321</v>
+        <v>20.99038333333336</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3848083333333321</v>
+        <v>20.99038333333336</v>
       </c>
       <c r="F8" t="n">
-        <v>8.083275119292232</v>
+        <v>236.4667064913405</v>
       </c>
       <c r="G8" t="n">
-        <v>6.858870098628831</v>
+        <v>215.4494197047185</v>
       </c>
     </row>
   </sheetData>
@@ -1870,25 +1869,25 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79898987322333</v>
+        <v>23.33452377915607</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11.25</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>27.75</v>
       </c>
       <c r="I2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1901,25 +1900,25 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.77836666666666</v>
+        <v>411.6189083333334</v>
       </c>
       <c r="D3" t="n">
-        <v>2.686392942631849</v>
+        <v>93.34126531202659</v>
       </c>
       <c r="E3" t="n">
-        <v>14.8788</v>
+        <v>345.6166666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82858333333333</v>
+        <v>378.6177875</v>
       </c>
       <c r="G3" t="n">
-        <v>16.77836666666666</v>
+        <v>411.6189083333334</v>
       </c>
       <c r="H3" t="n">
-        <v>17.72815</v>
+        <v>444.6200291666667</v>
       </c>
       <c r="I3" t="n">
-        <v>18.67793333333333</v>
+        <v>477.62115</v>
       </c>
     </row>
     <row r="4">
@@ -1932,25 +1931,25 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>23.206475</v>
+        <v>363.2403833333333</v>
       </c>
       <c r="D4" t="n">
-        <v>9.121712832645523</v>
+        <v>6.848965571894783</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75645</v>
+        <v>358.3974333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>19.9814625</v>
+        <v>360.8189083333333</v>
       </c>
       <c r="G4" t="n">
-        <v>23.206475</v>
+        <v>363.2403833333333</v>
       </c>
       <c r="H4" t="n">
-        <v>26.4314875</v>
+        <v>365.6618583333333</v>
       </c>
       <c r="I4" t="n">
-        <v>29.6565</v>
+        <v>368.0833333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1963,25 +1962,25 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>12.08119737013699</v>
+        <v>323.3988111875138</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9295391965330931</v>
+        <v>4.326505639859127</v>
       </c>
       <c r="E5" t="n">
-        <v>11.42391390088974</v>
+        <v>320.3395097107276</v>
       </c>
       <c r="F5" t="n">
-        <v>11.75255563551336</v>
+        <v>321.8691604491207</v>
       </c>
       <c r="G5" t="n">
-        <v>12.08119737013699</v>
+        <v>323.3988111875138</v>
       </c>
       <c r="H5" t="n">
-        <v>12.40983910476061</v>
+        <v>324.928461925907</v>
       </c>
       <c r="I5" t="n">
-        <v>12.73848083938423</v>
+        <v>326.4581126643001</v>
       </c>
     </row>
     <row r="6">
@@ -1994,25 +1993,25 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>12.14310176107847</v>
+        <v>323.6398177311509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7163319769575297</v>
+        <v>4.173060951487927</v>
       </c>
       <c r="E6" t="n">
-        <v>11.63657856259103</v>
+        <v>320.689018034049</v>
       </c>
       <c r="F6" t="n">
-        <v>11.88984016183475</v>
+        <v>322.1644178826</v>
       </c>
       <c r="G6" t="n">
-        <v>12.14310176107847</v>
+        <v>323.6398177311509</v>
       </c>
       <c r="H6" t="n">
-        <v>12.39636336032218</v>
+        <v>325.1152175797018</v>
       </c>
       <c r="I6" t="n">
-        <v>12.6496249595659</v>
+        <v>326.5906174282528</v>
       </c>
     </row>
     <row r="7">
@@ -2025,25 +2024,25 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>53.40795698019868</v>
+        <v>58.91096342759101</v>
       </c>
       <c r="D7" t="n">
-        <v>2.883542175094328</v>
+        <v>8.069210127916042</v>
       </c>
       <c r="E7" t="n">
-        <v>51.36898475435208</v>
+        <v>53.20517022732241</v>
       </c>
       <c r="F7" t="n">
-        <v>52.38847086727538</v>
+        <v>56.05806682745671</v>
       </c>
       <c r="G7" t="n">
-        <v>53.40795698019868</v>
+        <v>58.91096342759101</v>
       </c>
       <c r="H7" t="n">
-        <v>54.42744309312199</v>
+        <v>61.76386002772531</v>
       </c>
       <c r="I7" t="n">
-        <v>55.44692920604529</v>
+        <v>64.61675662785962</v>
       </c>
     </row>
     <row r="8">
@@ -2056,25 +2055,25 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>52.4412398695302</v>
+        <v>59.34158737420108</v>
       </c>
       <c r="D8" t="n">
-        <v>10.10680772945875</v>
+        <v>0.477337003953304</v>
       </c>
       <c r="E8" t="n">
-        <v>45.29464758788131</v>
+        <v>59.00405914179443</v>
       </c>
       <c r="F8" t="n">
-        <v>48.86794372870575</v>
+        <v>59.17282325799776</v>
       </c>
       <c r="G8" t="n">
-        <v>52.4412398695302</v>
+        <v>59.34158737420108</v>
       </c>
       <c r="H8" t="n">
-        <v>56.01453601035465</v>
+        <v>59.5103514904044</v>
       </c>
       <c r="I8" t="n">
-        <v>59.58783215117909</v>
+        <v>59.67911560660773</v>
       </c>
     </row>
     <row r="9">
@@ -2087,25 +2086,25 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.428108333333337</v>
+        <v>48.37852500000002</v>
       </c>
       <c r="D9" t="n">
-        <v>6.435319890013674</v>
+        <v>86.4922997401318</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.97856666666667</v>
+        <v>-12.78076666666664</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.703337500000005</v>
+        <v>17.79887916666669</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.428108333333337</v>
+        <v>48.37852500000002</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.152879166666668</v>
+        <v>78.95817083333336</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.877650000000001</v>
+        <v>109.5378166666667</v>
       </c>
     </row>
     <row r="10">
@@ -2118,25 +2117,25 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.06190439094147937</v>
+        <v>-0.2410065436370701</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2132072195755635</v>
+        <v>0.1534446883711995</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2126646617012895</v>
+        <v>-0.3495083233214018</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1372845263213844</v>
+        <v>-0.2952574334792359</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06190439094147937</v>
+        <v>-0.2410065436370701</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0134757444384257</v>
+        <v>-0.1867556537949042</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08885587981833076</v>
+        <v>-0.1325047639527384</v>
       </c>
     </row>
     <row r="11">
@@ -2149,25 +2148,25 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9667171106684833</v>
+        <v>-0.4306239466100656</v>
       </c>
       <c r="D11" t="n">
-        <v>7.223265554364418</v>
+        <v>7.591873123962738</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.140902945133803</v>
+        <v>-5.798888914472016</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.58709291723266</v>
+        <v>-3.114756430541041</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9667171106684833</v>
+        <v>-0.4306239466100656</v>
       </c>
       <c r="H11" t="n">
-        <v>3.520527138569626</v>
+        <v>2.25350853732091</v>
       </c>
       <c r="I11" t="n">
-        <v>6.074337166470769</v>
+        <v>4.937641021251885</v>
       </c>
     </row>
     <row r="12">
@@ -2180,25 +2179,25 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>-5.75</v>
+        <v>3.998333333333338</v>
       </c>
       <c r="D12" t="n">
-        <v>8.131727983645296</v>
+        <v>42.09406668403517</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.5</v>
+        <v>-25.76666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.625</v>
+        <v>-10.88416666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.75</v>
+        <v>3.998333333333338</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.875</v>
+        <v>18.88083333333334</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>33.76333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2211,25 +2210,25 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1.390643336333535</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>38.825</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>39.80833333333334</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="14">
@@ -2273,25 +2272,25 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1.390643336333535</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>38.825</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>39.31666666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>39.80833333333334</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="16">
@@ -2304,25 +2303,25 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.1977366617433377</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.1758372816234922</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.07340092752195768</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.1355687946326477</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1977366617433377</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.2599045288540277</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
     </row>
     <row r="17">
@@ -2366,25 +2365,25 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.1977366617433377</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.1758372816234922</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.07340092752195768</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.1355687946326477</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.1977366617433377</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.2599045288540277</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
     </row>
     <row r="19">
@@ -2397,25 +2396,25 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>3.275</v>
+        <v>28.70666666666667</v>
       </c>
       <c r="D19" t="n">
-        <v>4.631549416771886</v>
+        <v>25.65383402144795</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6375</v>
+        <v>19.63666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>3.275</v>
+        <v>28.70666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9125</v>
+        <v>37.77666666666667</v>
       </c>
       <c r="I19" t="n">
-        <v>6.55</v>
+        <v>46.84666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -2428,25 +2427,25 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>9.025</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>12.76327740041718</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>4.5125</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>9.025</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>13.5375</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>18.05</v>
+        <v>35.98333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -2459,25 +2458,25 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>-5.75</v>
+        <v>-7.276666666666657</v>
       </c>
       <c r="D21" t="n">
-        <v>8.131727983645296</v>
+        <v>25.65383402144795</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.5</v>
+        <v>-25.41666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.625</v>
+        <v>-16.34666666666666</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.75</v>
+        <v>-7.276666666666657</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.875</v>
+        <v>1.793333333333344</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>10.86333333333334</v>
       </c>
     </row>
     <row r="22">
@@ -2490,25 +2489,25 @@
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1081514425367872</v>
+        <v>0.5857158266820153</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1529492368257389</v>
+        <v>0.1641748302193809</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.4696266909337409</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0540757212683936</v>
+        <v>0.527671258807878</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1081514425367872</v>
+        <v>0.5857158266820153</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1622271638051808</v>
+        <v>0.6437603945561524</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2163028850735744</v>
+        <v>0.7018049624302896</v>
       </c>
     </row>
     <row r="23">
@@ -2521,25 +2520,25 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05490449910668165</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07764668727197067</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02745224955334083</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05490449910668165</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08235674866002247</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1098089982133633</v>
+        <v>0.3473404234144944</v>
       </c>
     </row>
     <row r="24">
@@ -2552,25 +2551,25 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05324694343010555</v>
+        <v>0.2383754032675208</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07530254955376824</v>
+        <v>0.1641748302193809</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.1222862675192465</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02662347171505277</v>
+        <v>0.1803308353933837</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05324694343010555</v>
+        <v>0.2383754032675208</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07987041514515832</v>
+        <v>0.296419971141658</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1064938868602111</v>
+        <v>0.3544645390157952</v>
       </c>
     </row>
     <row r="25">
@@ -2583,25 +2582,25 @@
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>11.625</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>16.44023266258723</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5.8125</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>11.625</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>17.4375</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="26">
@@ -2614,25 +2613,25 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="27">
@@ -2645,25 +2644,25 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>11.275</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>16.44023266258723</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>5.4625</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>11.275</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>17.0875</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="28">
@@ -2676,25 +2675,25 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.02277715891963458</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.03221176705647454</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.01138857945981729</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.02277715891963458</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.03416573837945187</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.04555431783926916</v>
       </c>
     </row>
     <row r="29">
@@ -2738,25 +2737,25 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.02277715891963458</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.03221176705647454</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.01138857945981729</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.02277715891963458</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.03416573837945187</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.04555431783926916</v>
       </c>
     </row>
     <row r="31">
@@ -2769,25 +2768,25 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>7.674999999999998</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>9.911280049631438</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>4.170833333333333</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>7.674999999999998</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>11.17916666666666</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>14.68333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -2800,25 +2799,25 @@
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04166666666666666</v>
+        <v>4.125</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05892556509887896</v>
+        <v>0.05892556509887938</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02083333333333333</v>
+        <v>4.104166666666666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04166666666666666</v>
+        <v>4.125</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0625</v>
+        <v>4.145833333333334</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.166666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -2831,25 +2830,25 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.04166666666666666</v>
+        <v>3.549999999999998</v>
       </c>
       <c r="D33" t="n">
-        <v>0.05892556509887896</v>
+        <v>9.85235448453256</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.08333333333333333</v>
+        <v>-3.416666666666667</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0625</v>
+        <v>0.06666666666666554</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.04166666666666666</v>
+        <v>3.549999999999998</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.02083333333333333</v>
+        <v>7.03333333333333</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>10.51666666666666</v>
       </c>
     </row>
     <row r="34">
@@ -2862,25 +2861,25 @@
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.8335578012854268</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.8045163973830435</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.2646788011201056</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.5491183012027663</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.8335578012854268</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.117997301368087</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1.402436801450748</v>
       </c>
     </row>
     <row r="35">
@@ -2893,25 +2892,25 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0.006240002012443305</v>
+        <v>0.4459877578430442</v>
       </c>
       <c r="D35" t="n">
-        <v>0.008824695475232729</v>
+        <v>0.01214293925204888</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.4374014031543842</v>
       </c>
       <c r="F35" t="n">
-        <v>0.003120001006221652</v>
+        <v>0.4416945804987142</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006240002012443305</v>
+        <v>0.4459877578430442</v>
       </c>
       <c r="H35" t="n">
-        <v>0.009360003018664957</v>
+        <v>0.4502809351873743</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01248000402488661</v>
+        <v>0.4545741125317043</v>
       </c>
     </row>
     <row r="36">
@@ -2924,25 +2923,25 @@
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.006240002012443305</v>
+        <v>0.3875700434423826</v>
       </c>
       <c r="D36" t="n">
-        <v>0.008824695475232729</v>
+        <v>0.7923734581309946</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.01248000402488661</v>
+        <v>-0.1727226020342786</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.009360003018664957</v>
+        <v>0.107423720704052</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.006240002012443305</v>
+        <v>0.3875700434423826</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.003120001006221652</v>
+        <v>0.6677163661807131</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.9478626889190437</v>
       </c>
     </row>
     <row r="37">
@@ -2955,25 +2954,25 @@
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>2.3</v>
+        <v>50.9</v>
       </c>
       <c r="D37" t="n">
-        <v>0.282842712474619</v>
+        <v>2.239171473757394</v>
       </c>
       <c r="E37" t="n">
-        <v>2.1</v>
+        <v>49.31666666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>50.10833333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3</v>
+        <v>50.9</v>
       </c>
       <c r="H37" t="n">
-        <v>2.4</v>
+        <v>51.69166666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>52.48333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -2986,25 +2985,25 @@
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>3.276933333333333</v>
+        <v>63.72685833333333</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01451925924036343</v>
+        <v>2.319039184692418</v>
       </c>
       <c r="E38" t="n">
-        <v>3.266666666666667</v>
+        <v>62.08705</v>
       </c>
       <c r="F38" t="n">
-        <v>3.2718</v>
+        <v>62.90695416666667</v>
       </c>
       <c r="G38" t="n">
-        <v>3.276933333333333</v>
+        <v>63.72685833333333</v>
       </c>
       <c r="H38" t="n">
-        <v>3.282066666666667</v>
+        <v>64.5467625</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2872</v>
+        <v>65.36666666666666</v>
       </c>
     </row>
     <row r="39">
@@ -3017,25 +3016,25 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.9769333333333334</v>
+        <v>-12.82685833333333</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2683234532342555</v>
+        <v>0.07986771093502408</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.166666666666667</v>
+        <v>-12.88333333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0718</v>
+        <v>-12.85509583333333</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9769333333333334</v>
+        <v>-12.82685833333333</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8820666666666667</v>
+        <v>-12.79862083333333</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7871999999999999</v>
+        <v>-12.77038333333333</v>
       </c>
     </row>
     <row r="40">
@@ -3048,25 +3047,25 @@
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>1.978260063177</v>
+        <v>44.95112484034511</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5733984037686295</v>
+        <v>2.655206248734808</v>
       </c>
       <c r="E40" t="n">
-        <v>1.57280616355066</v>
+        <v>43.07361049641583</v>
       </c>
       <c r="F40" t="n">
-        <v>1.77553311336383</v>
+        <v>44.01236766838047</v>
       </c>
       <c r="G40" t="n">
-        <v>1.978260063177</v>
+        <v>44.95112484034511</v>
       </c>
       <c r="H40" t="n">
-        <v>2.18098701299017</v>
+        <v>45.88988201230975</v>
       </c>
       <c r="I40" t="n">
-        <v>2.38371396280334</v>
+        <v>46.82863918427439</v>
       </c>
     </row>
     <row r="41">
@@ -3079,25 +3078,25 @@
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>2.824124134535072</v>
+        <v>59.40954309504603</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3263480259184264</v>
+        <v>1.413027957203261</v>
       </c>
       <c r="E41" t="n">
-        <v>2.59336123238131</v>
+        <v>58.41038144450143</v>
       </c>
       <c r="F41" t="n">
-        <v>2.708742683458191</v>
+        <v>58.90996226977373</v>
       </c>
       <c r="G41" t="n">
-        <v>2.824124134535072</v>
+        <v>59.40954309504603</v>
       </c>
       <c r="H41" t="n">
-        <v>2.939505585611954</v>
+        <v>59.90912392031834</v>
       </c>
       <c r="I41" t="n">
-        <v>3.054887036688835</v>
+        <v>60.40870474559063</v>
       </c>
     </row>
     <row r="42">
@@ -3110,25 +3109,25 @@
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.8458640713580725</v>
+        <v>-14.45841825470092</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2470503778502031</v>
+        <v>4.068234205938069</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.02055506883065</v>
+        <v>-17.3350942491748</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.9332095700943612</v>
+        <v>-15.89675625193786</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.8458640713580725</v>
+        <v>-14.45841825470092</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.7585185726217838</v>
+        <v>-13.02008025746398</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6711730738854951</v>
+        <v>-11.58174226022705</v>
       </c>
     </row>
     <row r="43">
@@ -3141,25 +3140,25 @@
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>2.983891666666667</v>
+        <v>44.85000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7770278567328772</v>
+        <v>0.377123616632819</v>
       </c>
       <c r="E43" t="n">
-        <v>2.43445</v>
+        <v>44.58333333333334</v>
       </c>
       <c r="F43" t="n">
-        <v>2.709170833333333</v>
+        <v>44.71666666666668</v>
       </c>
       <c r="G43" t="n">
-        <v>2.983891666666667</v>
+        <v>44.85000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2586125</v>
+        <v>44.98333333333333</v>
       </c>
       <c r="I43" t="n">
-        <v>3.533333333333333</v>
+        <v>45.11666666666667</v>
       </c>
     </row>
     <row r="44">
@@ -3172,25 +3171,25 @@
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>3.028208333333333</v>
+        <v>51.5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5729332694564001</v>
+        <v>1.367073110293995</v>
       </c>
       <c r="E44" t="n">
-        <v>2.623083333333333</v>
+        <v>50.53333333333333</v>
       </c>
       <c r="F44" t="n">
-        <v>2.825645833333333</v>
+        <v>51.01666666666667</v>
       </c>
       <c r="G44" t="n">
-        <v>3.028208333333333</v>
+        <v>51.5</v>
       </c>
       <c r="H44" t="n">
-        <v>3.230770833333333</v>
+        <v>51.98333333333333</v>
       </c>
       <c r="I44" t="n">
-        <v>3.433333333333333</v>
+        <v>52.46666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -3203,25 +3202,25 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.04431666666666656</v>
+        <v>-6.649999999999995</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2040945872764771</v>
+        <v>0.9899494936611756</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.1886333333333332</v>
+        <v>-7.350000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1164749999999999</v>
+        <v>-6.999999999999998</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.04431666666666656</v>
+        <v>-6.649999999999995</v>
       </c>
       <c r="H45" t="n">
-        <v>0.02784166666666676</v>
+        <v>-6.299999999999992</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1000000000000001</v>
+        <v>-5.949999999999989</v>
       </c>
     </row>
     <row r="46">
@@ -3234,25 +3233,25 @@
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>1.911510745130967</v>
+        <v>40.3411924071978</v>
       </c>
       <c r="D46" t="n">
-        <v>0.08542090541671524</v>
+        <v>2.280585258585206</v>
       </c>
       <c r="E46" t="n">
-        <v>1.851109043655713</v>
+        <v>38.72857510577813</v>
       </c>
       <c r="F46" t="n">
-        <v>1.88130989439334</v>
+        <v>39.53488375648796</v>
       </c>
       <c r="G46" t="n">
-        <v>1.911510745130967</v>
+        <v>40.3411924071978</v>
       </c>
       <c r="H46" t="n">
-        <v>1.941711595868594</v>
+        <v>41.14750105790764</v>
       </c>
       <c r="I46" t="n">
-        <v>1.971912446606221</v>
+        <v>41.95380970861748</v>
       </c>
     </row>
     <row r="47">
@@ -3265,25 +3264,25 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>2.398963026795434</v>
+        <v>47.98752675012891</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5988426052808203</v>
+        <v>0.7398702772546042</v>
       </c>
       <c r="E47" t="n">
-        <v>1.975517359737947</v>
+        <v>47.46435945988381</v>
       </c>
       <c r="F47" t="n">
-        <v>2.187240193266691</v>
+        <v>47.72594310500636</v>
       </c>
       <c r="G47" t="n">
-        <v>2.398963026795434</v>
+        <v>47.98752675012891</v>
       </c>
       <c r="H47" t="n">
-        <v>2.610685860324177</v>
+        <v>48.24911039525146</v>
       </c>
       <c r="I47" t="n">
-        <v>2.822408693852921</v>
+        <v>48.51069404037401</v>
       </c>
     </row>
     <row r="48">
@@ -3296,25 +3295,25 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.4874522816644671</v>
+        <v>-7.646334342931109</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5134216998641051</v>
+        <v>3.02045553583981</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.8504962472467001</v>
+        <v>-9.782118934595886</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6689742644555836</v>
+        <v>-8.714226638763497</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.4874522816644671</v>
+        <v>-7.646334342931109</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.3059302988733505</v>
+        <v>-6.57844204709872</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.124408316082234</v>
+        <v>-5.510549751266332</v>
       </c>
     </row>
     <row r="49">
@@ -3327,25 +3326,25 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>8.219474999999999</v>
+        <v>228.545575</v>
       </c>
       <c r="D49" t="n">
-        <v>3.005027043347531</v>
+        <v>37.3289801516362</v>
       </c>
       <c r="E49" t="n">
-        <v>6.0946</v>
+        <v>202.15</v>
       </c>
       <c r="F49" t="n">
-        <v>7.157037499999999</v>
+        <v>215.3477875</v>
       </c>
       <c r="G49" t="n">
-        <v>8.219474999999999</v>
+        <v>228.545575</v>
       </c>
       <c r="H49" t="n">
-        <v>9.281912500000001</v>
+        <v>241.7433625</v>
       </c>
       <c r="I49" t="n">
-        <v>10.34435</v>
+        <v>254.94115</v>
       </c>
     </row>
     <row r="50">
@@ -3358,25 +3357,25 @@
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>7.834666666666668</v>
+        <v>207.5551916666666</v>
       </c>
       <c r="D50" t="n">
-        <v>4.170091531369548</v>
+        <v>3.10392771180952</v>
       </c>
       <c r="E50" t="n">
-        <v>4.885966666666667</v>
+        <v>205.3603833333333</v>
       </c>
       <c r="F50" t="n">
-        <v>6.360316666666668</v>
+        <v>206.4577875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.834666666666668</v>
+        <v>207.5551916666666</v>
       </c>
       <c r="H50" t="n">
-        <v>9.309016666666668</v>
+        <v>208.6525958333333</v>
       </c>
       <c r="I50" t="n">
-        <v>10.78336666666667</v>
+        <v>209.75</v>
       </c>
     </row>
     <row r="51">
@@ -3389,25 +3388,25 @@
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3848083333333321</v>
+        <v>20.99038333333336</v>
       </c>
       <c r="D51" t="n">
-        <v>1.165064488022017</v>
+        <v>34.22505243982668</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4390166666666691</v>
+        <v>-3.210383333333283</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.02710416666666848</v>
+        <v>8.890000000000036</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3848083333333321</v>
+        <v>20.99038333333336</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7967208333333327</v>
+        <v>33.09076666666667</v>
       </c>
       <c r="I51" t="n">
-        <v>1.208633333333333</v>
+        <v>45.19114999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3420,25 +3419,25 @@
         <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>8.083275119292232</v>
+        <v>236.4667064913405</v>
       </c>
       <c r="D52" t="n">
-        <v>1.741307742544173</v>
+        <v>8.437231434143827</v>
       </c>
       <c r="E52" t="n">
-        <v>6.851984606406608</v>
+        <v>230.5006829298171</v>
       </c>
       <c r="F52" t="n">
-        <v>7.46762986284942</v>
+        <v>233.4836947105788</v>
       </c>
       <c r="G52" t="n">
-        <v>8.083275119292232</v>
+        <v>236.4667064913405</v>
       </c>
       <c r="H52" t="n">
-        <v>8.698920375735042</v>
+        <v>239.4497182721022</v>
       </c>
       <c r="I52" t="n">
-        <v>9.314565632177855</v>
+        <v>242.4327300528639</v>
       </c>
     </row>
     <row r="53">
@@ -3451,25 +3450,25 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>6.858870098628831</v>
+        <v>215.4494197047185</v>
       </c>
       <c r="D53" t="n">
-        <v>1.710344599953513</v>
+        <v>2.008019777778049</v>
       </c>
       <c r="E53" t="n">
-        <v>5.649473833835908</v>
+        <v>214.0295353030949</v>
       </c>
       <c r="F53" t="n">
-        <v>6.254171966232369</v>
+        <v>214.7394775039067</v>
       </c>
       <c r="G53" t="n">
-        <v>6.858870098628831</v>
+        <v>215.4494197047185</v>
       </c>
       <c r="H53" t="n">
-        <v>7.463568231025292</v>
+        <v>216.1593619055302</v>
       </c>
       <c r="I53" t="n">
-        <v>8.068266363421753</v>
+        <v>216.869304106342</v>
       </c>
     </row>
     <row r="54">
@@ -3482,25 +3481,25 @@
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>1.224405020663401</v>
+        <v>21.01728678662204</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0309631425906592</v>
+        <v>6.429211656365779</v>
       </c>
       <c r="E54" t="n">
-        <v>1.2025107725707</v>
+        <v>16.4711476267222</v>
       </c>
       <c r="F54" t="n">
-        <v>1.213457896617051</v>
+        <v>18.74421720667212</v>
       </c>
       <c r="G54" t="n">
-        <v>1.224405020663401</v>
+        <v>21.01728678662204</v>
       </c>
       <c r="H54" t="n">
-        <v>1.235352144709752</v>
+        <v>23.29035636657196</v>
       </c>
       <c r="I54" t="n">
-        <v>1.246299268756102</v>
+        <v>25.56342594652187</v>
       </c>
     </row>
   </sheetData>
@@ -3559,64 +3558,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>16.77836666666666</v>
+        <v>411.6189083333334</v>
       </c>
       <c r="D2" t="n">
-        <v>23.206475</v>
+        <v>363.2403833333333</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.428108333333337</v>
+        <v>48.37852500000002</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.428108333333337</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>16_clustered_phase_heatmap.png</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Constant phase dimensions omitted: charging_refueling_time_diff_min, idle_time_diff_min</t>
-        </is>
+        <v>48.37852500000002</v>
       </c>
     </row>
   </sheetData>
